--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_242_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_242_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2063</v>
+        <v>10.0347</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2552</v>
+        <v>7.8148</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9511</v>
+        <v>2.2199</v>
       </c>
       <c r="G2" t="n">
         <v>7.4029</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8909</v>
+        <v>0.7194</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3645</v>
+        <v>0.9241</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4736</v>
+        <v>-0.2047</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3448</v>
+        <v>5.5539</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0332</v>
+        <v>3.1079</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3116</v>
+        <v>2.4461</v>
       </c>
       <c r="G3" t="n">
         <v>2.4926</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6203</v>
+        <v>0.8294</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395</v>
+        <v>0.1142</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5808</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.845</v>
+        <v>4.4416</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6309</v>
+        <v>3.0594</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2141</v>
+        <v>1.3822</v>
       </c>
       <c r="G4" t="n">
         <v>1.9086</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8316</v>
+        <v>-0.235</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>-0.3183</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0848</v>
+        <v>0.0833</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4565</v>
+        <v>3.5066</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5274</v>
+        <v>1.4095</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9291</v>
+        <v>2.0971</v>
       </c>
       <c r="G5" t="n">
         <v>2.9682</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5759</v>
+        <v>0.626</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>0.387</v>
+        <v>0.5551</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7716</v>
+        <v>2.5558</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4206</v>
+        <v>0.6832</v>
       </c>
       <c r="F6" t="n">
-        <v>2.351</v>
+        <v>1.8726</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2941</v>
+        <v>3.7835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1693</v>
+        <v>2.1742</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1248</v>
+        <v>1.6094</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3757</v>
+        <v>1.8074</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.6637</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2882</v>
+        <v>0.1437</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9184</v>
+        <v>1.9762</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0818</v>
+        <v>0.5105</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8366</v>
+        <v>1.4657</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8692</v>
+        <v>-0.1555</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3645</v>
+        <v>0.2675</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5048</v>
+        <v>-0.423</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5569</v>
+        <v>1.5912</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2485</v>
+        <v>-0.2557</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8054</v>
+        <v>1.8469</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7835</v>
+        <v>2.2941</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1742</v>
+        <v>0.1693</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6094</v>
+        <v>2.1248</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8074</v>
+        <v>1.3757</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6637</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1437</v>
+        <v>1.2882</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9762</v>
+        <v>0.9184</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5105</v>
+        <v>0.0818</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4657</v>
+        <v>0.8366</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1545</v>
+        <v>0.6888</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>0.6882</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4902</v>
+        <v>0.0007</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0105</v>
+        <v>1.4144</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8804</v>
+        <v>-1.6445</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8909</v>
+        <v>3.0589</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6503</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.972</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8588</v>
+        <v>1.0269</v>
       </c>
       <c r="V8" t="n">
         <v>1.3247</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0873</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4856</v>
+        <v>0.635</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5813</v>
+        <v>-0.5477</v>
       </c>
       <c r="G9" t="n">
         <v>1.3488</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.532</v>
+        <v>-0.349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2161</v>
+        <v>-0.0668</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3159</v>
+        <v>-0.2822</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3146</v>
+        <v>-1.0451</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0021</v>
+        <v>-2.7662</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6875</v>
+        <v>1.7212</v>
       </c>
       <c r="G10" t="n">
         <v>-0.468</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5452</v>
+        <v>0.8147</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3462</v>
+        <v>0.5821</v>
       </c>
       <c r="U10" t="n">
-        <v>0.199</v>
+        <v>0.2326</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9672</v>
+        <v>-2.1972</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4701</v>
+        <v>-3.364</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5028</v>
+        <v>1.1668</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7244</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8294</v>
+        <v>0.5994</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4288</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4007</v>
+        <v>0.0646</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4414</v>
+        <v>-4.4504</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.711</v>
+        <v>-4.5184</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2697</v>
+        <v>0.068</v>
       </c>
       <c r="G12" t="n">
         <v>0.655</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6871</v>
+        <v>0.6781</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9858</v>
+        <v>0.7842</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.3727</v>
+        <v>21.4928</v>
       </c>
       <c r="E13" t="n">
-        <v>3.040799999999999</v>
+        <v>4.160999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>17.3319</v>
+        <v>17.332</v>
       </c>
       <c r="G13" t="n">
         <v>18.011</v>
@@ -1468,13 +1468,13 @@
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0679</v>
+        <v>5.1883</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5158</v>
+        <v>2.6357</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5524</v>
+        <v>2.5527</v>
       </c>
       <c r="V13" t="n">
         <v>2.933</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7749</v>
+        <v>2.7061</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9093</v>
+        <v>0.2998</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8656</v>
+        <v>2.4062</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0819</v>
+        <v>1.4784</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0491</v>
+        <v>-2.0683</v>
       </c>
       <c r="I14" t="n">
-        <v>1.131</v>
+        <v>3.5467</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3179</v>
+        <v>1.5576</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6554</v>
+        <v>-1.1526</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6625</v>
+        <v>2.7101</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.236</v>
+        <v>-0.0791</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7045</v>
+        <v>-0.9157</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4685</v>
+        <v>0.8366</v>
       </c>
       <c r="P14" t="n">
         <v>2.0876</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3945</v>
+        <v>-0.8599</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1766</v>
+        <v>-1.0258</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2179</v>
+        <v>0.1658</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6826</v>
+        <v>2.6899</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0639</v>
+        <v>0.5555</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6186</v>
+        <v>2.1345</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4784</v>
+        <v>1.0819</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.0683</v>
+        <v>-0.0491</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5467</v>
+        <v>1.131</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5576</v>
+        <v>1.3179</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1526</v>
+        <v>0.6554</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7101</v>
+        <v>0.6625</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0791</v>
+        <v>-0.236</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9157</v>
+        <v>-0.7045</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8366</v>
+        <v>0.4685</v>
       </c>
       <c r="P15" t="n">
         <v>2.0876</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8834</v>
+        <v>-0.4795</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>-0.5305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3782</v>
+        <v>0.051</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.991</v>
+        <v>1.031</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6097</v>
+        <v>0.7277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3813</v>
+        <v>0.3033</v>
       </c>
       <c r="G16" t="n">
         <v>0.4678</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1726</v>
+        <v>-0.1327</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1182</v>
+        <v>0.0402</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1073</v>
+        <v>-0.9937</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4011</v>
+        <v>-1.8126</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2937</v>
+        <v>0.8188</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2372</v>
+        <v>-0.698</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.384</v>
+        <v>1.8952</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8532</v>
+        <v>-2.5932</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9717</v>
+        <v>0.1491</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3326</v>
+        <v>2.632</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6391</v>
+        <v>-2.4829</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2655</v>
+        <v>-0.8472</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0514</v>
+        <v>-0.7369</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.214</v>
+        <v>-0.1103</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4938</v>
+        <v>-1.1154</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0376</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5439000000000001</v>
+        <v>-0.2076</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4975</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7716</v>
+        <v>-1.101</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3044</v>
+        <v>-3.2831</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4672</v>
+        <v>2.1822</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0153</v>
+        <v>-2.2372</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4875</v>
+        <v>-1.384</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4722</v>
+        <v>-0.8532</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0428</v>
+        <v>-0.9717</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4145</v>
+        <v>-0.3326</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3717</v>
+        <v>-0.6391</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9725</v>
+        <v>-1.2655</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.073</v>
+        <v>-1.0514</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1005</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5398</v>
+        <v>-0.4874</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0297</v>
+        <v>-0.9197</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.51</v>
+        <v>0.4323</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8073</v>
+        <v>-1.1153</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1664</v>
+        <v>-0.9506</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3591</v>
+        <v>-0.1647</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.698</v>
+        <v>-1.0153</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8952</v>
+        <v>-2.4875</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5932</v>
+        <v>1.4722</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1491</v>
+        <v>-0.0428</v>
       </c>
       <c r="K19" t="n">
-        <v>2.632</v>
+        <v>-1.4145</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.4829</v>
+        <v>1.3717</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8472</v>
+        <v>-0.9725</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7369</v>
+        <v>-1.073</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1103</v>
+        <v>0.1005</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.929</v>
+        <v>-0.8834</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2617</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6673</v>
+        <v>-0.2076</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8197</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>D. MUTAF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7127</v>
+        <v>-2.5756</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7571</v>
+        <v>-1.7134</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0444</v>
+        <v>-0.8622</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.2282</v>
+        <v>-2.4922</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8693</v>
+        <v>0.7635</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3589</v>
+        <v>-3.2557</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.2205</v>
+        <v>-1.5524</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.076</v>
+        <v>0.8066</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1445</v>
+        <v>-2.359</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0077</v>
+        <v>-0.9398</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2067</v>
+        <v>-0.0431</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2144</v>
+        <v>-0.8966</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2113</v>
+        <v>-0.0835</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.0709</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3396</v>
+        <v>-0.1544</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MUTAF</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1876</v>
+        <v>-2.8364</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0673</v>
+        <v>-3.229</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1203</v>
+        <v>0.3926</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4922</v>
+        <v>-6.2282</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7635</v>
+        <v>-3.8693</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.2557</v>
+        <v>-2.3589</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5524</v>
+        <v>-5.2205</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8066</v>
+        <v>-4.076</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.359</v>
+        <v>-1.1445</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9398</v>
+        <v>-1.0077</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0431</v>
+        <v>0.2067</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8966</v>
+        <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6954</v>
+        <v>0.0876</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>0.0791</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4125</v>
+        <v>0.0086</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1911</v>
+        <v>-2.9831</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7513</v>
+        <v>-3.6333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5602</v>
+        <v>0.6502</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9683</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1353</v>
+        <v>0.0727</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0905</v>
+        <v>0.2084</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2258</v>
+        <v>-0.1357</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6232</v>
+        <v>-3.8419</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7974</v>
+        <v>-0.9154</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8257</v>
+        <v>-2.9265</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5075</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6524</v>
+        <v>0.4336</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2715</v>
+        <v>0.1535</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3809</v>
+        <v>0.2801</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8236</v>
+        <v>-4.749</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0949</v>
+        <v>-1.449</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7286</v>
+        <v>-3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4444</v>
+        <v>-2.4479</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6544</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.79</v>
+        <v>-3.3627</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7794</v>
+        <v>-0.4468</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7794</v>
+        <v>1.1259</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1.5727</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6651</v>
+        <v>-2.0012</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1249</v>
+        <v>-0.2112</v>
       </c>
       <c r="O24" t="n">
         <v>-1.79</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>1.925</v>
+        <v>0.235</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0761</v>
+        <v>0.3894</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1511</v>
+        <v>-0.1544</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5969</v>
+        <v>-5.031</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0388</v>
+        <v>-1.3924</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.5581</v>
+        <v>-3.6386</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4479</v>
+        <v>-2.4444</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9147999999999999</v>
+        <v>-0.6544</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.3627</v>
+        <v>-1.79</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4468</v>
+        <v>-0.7794</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1259</v>
+        <v>-0.7794</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5727</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0012</v>
+        <v>-1.6651</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2112</v>
+        <v>0.1249</v>
       </c>
       <c r="O25" t="n">
         <v>-1.79</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6128</v>
+        <v>0.7176</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2003</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4125</v>
+        <v>-0.0611</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-20.3728</v>
+        <v>-18.8</v>
       </c>
       <c r="E26" t="n">
         <v>-16.7958</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.577000000000001</v>
+        <v>-2.004199999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-18.0109</v>
@@ -2458,7 +2458,7 @@
         <v>-6.287999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5488000000000006</v>
+        <v>-0.5488000000000005</v>
       </c>
       <c r="L26" t="n">
         <v>-5.7393</v>
@@ -2467,13 +2467,13 @@
         <v>-11.7231</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.8481</v>
+        <v>-4.848099999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-6.8748</v>
       </c>
       <c r="P26" t="n">
-        <v>4.639099999999999</v>
+        <v>4.639100000000002</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.5978</v>
@@ -2482,13 +2482,13 @@
         <v>16.2369</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0679</v>
+        <v>-2.4953</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.552300000000002</v>
+        <v>-2.552599999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5155</v>
+        <v>0.05720000000000004</v>
       </c>
       <c r="V26" t="n">
         <v>-2.933</v>
